--- a/03_test-cases/v1.0/fragments/TC-NTF-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-NTF-v1.0.xlsx
@@ -1480,7 +1480,7 @@
       </c>
       <c r="AP8" s="69" t="inlineStr">
         <is>
-          <t>Technique: BVA-min-1 (test lần thứ N-1=2, N=3 giá trị mock — C-NTF-02 Partially Resolved, ngưỡng thật chưa chốt số)</t>
+          <t>Technique: BVA-min-1 (dưới ngưỡng: 3 tin phù hợp / trần 5) | Trần 5 thông báo cho MỖI tin OFFER — OPR-01 / REQ-ASN-005 / SC-ASN-013, BA xác nhận qua chat 2026-07-29 (KHÔNG có ngưỡng theo ngày; SC-NTF-006 đã DEPRECATED). Test data 3/5/6 tin là giá trị chốt, không còn là mock</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AP9" s="69" t="inlineStr">
         <is>
-          <t>Technique: BVA-max (test đúng tại ngưỡng N=3 giá trị mock — C-NTF-02 Partially Resolved, ngưỡng thật chưa chốt số)</t>
+          <t>Technique: BVA-max (đúng tại ngưỡng: 5 tin phù hợp / trần 5) | Trần 5 thông báo cho MỖI tin OFFER — OPR-01 / REQ-ASN-005 / SC-ASN-013, BA xác nhận qua chat 2026-07-29. Test data là giá trị chốt, không còn là mock</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AP10" s="69" t="inlineStr">
         <is>
-          <t>Technique: BVA-max+1 (vượt ngưỡng N=3 mock) | Ngưỡng cụ thể (bao nhiêu lần/ngày) vẫn Open (C-NTF-02, Partially Resolved) — cần BA chốt số trước khi coi test data là final</t>
+          <t>Technique: BVA-max+1 (vượt ngưỡng: 6 tin phù hợp / trần 5) | Trần 5 thông báo cho MỖI tin OFFER — OPR-01 / REQ-ASN-005 / SC-ASN-013, BA xác nhận qua chat 2026-07-29. Ngưỡng đã CHỐT, không còn Open; test data 6 tin là giá trị chốt, không phải mock</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C16" s="64" t="inlineStr">
         <is>
-          <t>Chờ BA bổ sung</t>
+          <t>DOC-v1.0-01 §D1b (US-D09) + §D6 (NTF)</t>
         </is>
       </c>
       <c r="D16" s="64" t="inlineStr">
@@ -2196,23 +2196,23 @@
       </c>
       <c r="F16" s="65" t="inlineStr">
         <is>
-          <t>Check hệ thống KHÔNG cho phép bỏ qua bước "Đã lấy hàng" (skip-step)</t>
+          <t>Check KHÔNG phát sinh thông báo "Đơn đã được giao" khi Carrier bỏ qua bước "Đã lấy hàng"</t>
         </is>
       </c>
       <c r="G16" s="65" t="inlineStr">
         <is>
-          <t>Đơn đang ở trạng thái MATCHED (chưa qua IN_TRANSIT, chưa từng bấm "Tôi đã lấy hàng")</t>
+          <t>Đơn đang ở trạng thái MATCHED (đã ghép, Carrier CHƯA bấm "Tôi đã lấy hàng")</t>
         </is>
       </c>
       <c r="H16" s="65" t="inlineStr">
         <is>
           <t>1. Carrier cố thực hiện "Đã giao cho người nhận" khi đơn còn đang MATCHED
-2. Quan sát phản hồi hệ thống + màn Thông báo của Sender/Receiver</t>
+2. Mở màn Thông báo của Sender và của Receiver</t>
         </is>
       </c>
       <c r="I16" s="65" t="inlineStr">
         <is>
-          <t>2. Hệ thống KHÔNG cho phép chuyển thẳng MATCHED→DELIVERED (nút "Đã giao" bị disable hoặc báo lỗi); KHÔNG phát sinh thông báo "Đơn đã được giao" khi chưa qua bước lấy hàng</t>
+          <t>2. Cả Sender và Receiver đều KHÔNG nhận được thông báo "Đơn đã được giao" — danh sách thông báo không phát sinh item mới nào cho sự kiện này</t>
         </is>
       </c>
       <c r="J16" s="64" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AP16" s="69" t="inlineStr">
         <is>
-          <t>Technique: ST-invalid-MATCHED-DELIVERED (skip-step)</t>
+          <t>Technique: ST-invalid-MATCHED-DELIVERED (chỉ assert vế THÔNG BÁO) | Dedupe: vế chặn transition + trạng thái nút trên màn Theo dõi đơn đã cover tại TC_07.16 (SC-DLV-006) — không lặp lại ở sheet Thông báo | Viết lại 2026-07-30 theo finding review-tc m8 (R4-08)</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="C18" s="40" t="inlineStr">
         <is>
-          <t>Chờ BA bổ sung</t>
+          <t>DOC-v1.0-01 §A5 (BR-CNF-04) + §D6 (NTF)</t>
         </is>
       </c>
       <c r="D18" s="40" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="F18" s="72" t="inlineStr">
         <is>
-          <t>Check Receiver KHÔNG xác nhận được "Đã nhận hàng" khi đơn chưa ở trạng thái Đã giao</t>
+          <t>Check KHÔNG phát sinh thông báo "Đơn đã hoàn tất" khi Receiver xác nhận lúc đơn chưa "Đã giao"</t>
         </is>
       </c>
       <c r="G18" s="72" t="inlineStr">
@@ -2419,12 +2419,12 @@
       <c r="H18" s="72" t="inlineStr">
         <is>
           <t>1. Receiver cố thực hiện "Xác nhận đã nhận hàng" khi đơn chưa DELIVERED
-2. Quan sát phản hồi hệ thống</t>
+2. Mở màn Thông báo của Sender và của Carrier</t>
         </is>
       </c>
       <c r="I18" s="72" t="inlineStr">
         <is>
-          <t>2. Hệ thống KHÔNG cho phép xác nhận (nút ẩn/disable hoặc báo lỗi); KHÔNG phát sinh thông báo "Đơn đã hoàn tất"</t>
+          <t>2. Cả Sender và Carrier đều KHÔNG nhận được thông báo "Đơn đã hoàn tất — cảm ơn bạn" — danh sách thông báo không phát sinh item mới nào cho sự kiện này</t>
         </is>
       </c>
       <c r="J18" s="62" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AP18" s="60" t="inlineStr">
         <is>
-          <t>Technique: ST-invalid-notDELIVERED-COMPLETED (skip-step)</t>
+          <t>Technique: ST-invalid-notDELIVERED-COMPLETED (chỉ assert vế THÔNG BÁO) | Dedupe: vế nút "Xác nhận đã nhận hàng" bị động ở 3 trạng thái đã cover tại TC_07.8/TC_07.9/TC_07.10 (SC-DLV-005) — không lặp lại ở sheet Thông báo | Viết lại 2026-07-30 theo finding review-tc m8 (R4-08)</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="C23" s="64" t="inlineStr">
         <is>
-          <t>Chờ BA bổ sung</t>
+          <t>DOC-v1.0-01 §D6 + DOC-v1.0-04 · Chờ BA — C-NTF-01 (Open)</t>
         </is>
       </c>
       <c r="D23" s="64" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="C24" s="64" t="inlineStr">
         <is>
-          <t>Chờ BA bổ sung</t>
+          <t>DOC-v1.0-01 §D6 + DOC-v1.0-04 · Chờ BA — C-NTF-01 (Open)</t>
         </is>
       </c>
       <c r="D24" s="64" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
-          <t>Chờ BA bổ sung</t>
+          <t>QA xác nhận app STG (2026-07-28) · C-ORD-06 Resolved (mở rộng sang màn Thông báo)</t>
         </is>
       </c>
       <c r="D29" s="40" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="C31" s="64" t="inlineStr">
         <is>
-          <t>DOC-v1.0-04 / QA đề xuất hành vi</t>
+          <t>DOC-v1.0-04 · QA đề xuất — Chờ BA/Dev — C-NTF-03 (Open)</t>
         </is>
       </c>
       <c r="D31" s="64" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="F31" s="65" t="inlineStr">
         <is>
-          <t>Check tap vào 1 thông báo cụ thể chuyển đúng trạng thái đã đọc (không ảnh hưởng thông báo khác)</t>
+          <t>Check bấm vào 1 thông báo cụ thể chuyển đúng trạng thái đã đọc (không ảnh hưởng thông báo khác)</t>
         </is>
       </c>
       <c r="G31" s="65" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C32" s="64" t="inlineStr">
         <is>
-          <t>DOC-v1.0-04 / QA đề xuất hành vi</t>
+          <t>DOC-v1.0-04 · QA đề xuất — Chờ BA/Dev — C-NTF-03 (Open)</t>
         </is>
       </c>
       <c r="D32" s="64" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="C33" s="64" t="inlineStr">
         <is>
-          <t>QA đề xuất hành vi</t>
+          <t>QA đề xuất — Chờ BA/Dev — C-NTF-03 (Open)</t>
         </is>
       </c>
       <c r="D33" s="64" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="F33" s="65" t="inlineStr">
         <is>
-          <t>Check tap vào 1 thông báo ĐÃ đọc không gây lỗi và không đổi trạng thái thông báo khác</t>
+          <t>Check bấm vào 1 thông báo ĐÃ đọc không gây lỗi và không đổi trạng thái thông báo khác</t>
         </is>
       </c>
       <c r="G33" s="65" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="C34" s="64" t="inlineStr">
         <is>
-          <t>QA đề xuất hành vi</t>
+          <t>QA đề xuất — Chờ BA/Dev — C-NTF-03 (Open)</t>
         </is>
       </c>
       <c r="D34" s="64" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C36" s="64" t="inlineStr">
         <is>
-          <t>UI nền tảng (scroll-load)</t>
+          <t>QA xác nhận app STG (2026-07-28) · C-NTF-03 Resolved (cơ chế phân trang)</t>
         </is>
       </c>
       <c r="D36" s="64" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="C37" s="64" t="inlineStr">
         <is>
-          <t>UI nền tảng (scroll-load)</t>
+          <t>UI nền tảng (scroll-load) · QA đề xuất — Chờ BA/Dev — C-NTF-03 (Open)</t>
         </is>
       </c>
       <c r="D37" s="64" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C38" s="64" t="inlineStr">
         <is>
-          <t>UI nền tảng (scroll-load)</t>
+          <t>UI nền tảng (scroll-load) · QA đề xuất — Chờ BA/Dev — C-NTF-03 (Open)</t>
         </is>
       </c>
       <c r="D38" s="64" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="C39" s="64" t="inlineStr">
         <is>
-          <t>UI nền tảng (scroll-load)</t>
+          <t>UI nền tảng (scroll-load) · QA đề xuất — Chờ BA/Dev — C-NTF-03 (Open)</t>
         </is>
       </c>
       <c r="D39" s="64" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="C40" s="64" t="inlineStr">
         <is>
-          <t>UI nền tảng (scroll-load)</t>
+          <t>UI nền tảng (scroll-load) · QA đề xuất — Chờ BA/Dev — C-NTF-03 (Open)</t>
         </is>
       </c>
       <c r="D40" s="64" t="inlineStr">
@@ -9151,17 +9151,17 @@
     <row r="7" ht="15" customHeight="1" s="41">
       <c r="A7" s="80" t="inlineStr">
         <is>
-          <t>SC-NTF-006</t>
+          <t>SC-ASN-013</t>
         </is>
       </c>
       <c r="B7" s="81" t="inlineStr">
         <is>
-          <t>Carrier bị giới hạn trần thông báo khớp/ngày</t>
+          <t>Hệ thống chỉ bắn tối đa 5 thông báo khớp tin cho Carrier, tính riêng theo TỪNG TIN — không cộng dồn theo ngày</t>
         </is>
       </c>
       <c r="C7" s="81" t="inlineStr">
         <is>
-          <t>DOC-v1.0-01 §D7 "OPR-06 Trần thông báo khớp/ngày..."</t>
+          <t>DOC-v1.0-01 §D7 "OPR-01" + BA xác nhận qua chat 2026-07-29 (thay thế SC-NTF-006, DEPRECATED)</t>
         </is>
       </c>
       <c r="D7" s="79" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="E7" s="78" t="inlineStr">
         <is>
-          <t>✅ 3 (min-1/at-cap/max+1)</t>
+          <t>✅ 3 (BVA-min-1 / max / max+1 quanh trần 5)</t>
         </is>
       </c>
       <c r="F7" s="79" t="inlineStr">
@@ -9411,7 +9411,7 @@
     <row r="12" ht="15" customHeight="1" s="41">
       <c r="A12" s="82" t="inlineStr">
         <is>
-          <t>Total scenarios: 9</t>
+          <t>Total scenarios: 9 (8 NTF còn hiệu lực + SC-ASN-013; SC-NTF-006 đã DEPRECATED 2026-07-29 nên không còn row riêng)</t>
         </is>
       </c>
     </row>

--- a/03_test-cases/v1.0/fragments/TC-NTF-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-NTF-v1.0.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Thông báo" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Coverage Matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>

--- a/03_test-cases/v1.0/fragments/TC-NTF-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-NTF-v1.0.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Coverage Matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$6:$U$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Thông báo'!$A$6:$U$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Coverage Matrix'!$A$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -2594,10 +2594,7 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="41">
-      <c r="A20" s="64">
-        <f>IF(C20="","",$C$2&amp;"."&amp;COUNTA($C$8:C20)&amp;"")</f>
-        <v/>
-      </c>
+      <c r="A20" s="64" t="n"/>
       <c r="B20" s="64" t="n"/>
       <c r="C20" s="64" t="n"/>
       <c r="D20" s="64" t="n"/>
@@ -3339,22 +3336,67 @@
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="41">
-      <c r="A28" s="64" t="n"/>
-      <c r="B28" s="70" t="inlineStr">
-        <is>
-          <t>Block Empty state (không có thông báo nào)</t>
-        </is>
-      </c>
-      <c r="C28" s="46" t="n"/>
-      <c r="D28" s="46" t="n"/>
-      <c r="E28" s="46" t="n"/>
-      <c r="F28" s="46" t="n"/>
-      <c r="G28" s="46" t="n"/>
-      <c r="H28" s="46" t="n"/>
-      <c r="I28" s="44" t="n"/>
-      <c r="J28" s="64" t="n"/>
-      <c r="K28" s="64" t="n"/>
-      <c r="L28" s="64" t="n"/>
+      <c r="A28" s="64">
+        <f>IF(C28="","",$C$2&amp;"."&amp;COUNTA($C$8:C28)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B28" s="64" t="inlineStr">
+        <is>
+          <t>REQ-NTF-001</t>
+        </is>
+      </c>
+      <c r="C28" s="64" t="inlineStr">
+        <is>
+          <t>Quan sát thực tế app STG (QA GiangDC2, chat 2026-07-30)</t>
+        </is>
+      </c>
+      <c r="D28" s="64" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E28" s="64" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F28" s="65" t="inlineStr">
+        <is>
+          <t>Check icon quay lại tại màn Thông báo</t>
+        </is>
+      </c>
+      <c r="G28" s="65" t="inlineStr">
+        <is>
+          <t>Đã đăng nhập app FoxEco, đang ở Trang chủ</t>
+        </is>
+      </c>
+      <c r="H28" s="65" t="inlineStr">
+        <is>
+          <t>1. Mở app FoxEco
+2. Bấm icon chuông tại Header (ở Trang chủ) để mở màn Thông báo
+3. Bấm icon quay lại (←) ở Header</t>
+        </is>
+      </c>
+      <c r="I28" s="65" t="inlineStr">
+        <is>
+          <t>3. Điều hướng đúng về màn đã mở Thông báo từ đó (Trang chủ)</t>
+        </is>
+      </c>
+      <c r="J28" s="64" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K28" s="64" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L28" s="64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="M28" s="64" t="n"/>
       <c r="N28" s="66" t="n"/>
       <c r="O28" s="66" t="n"/>
@@ -3382,80 +3424,40 @@
       <c r="AK28" s="67" t="n"/>
       <c r="AL28" s="67" t="n"/>
       <c r="AM28" s="68">
-        <f>IF($A28="","",IF(OR($N28="Yes",$S28="Yes",$X28="Yes",$AC28="Yes",$AH28="Yes"),"Yes","No"))</f>
+        <f>IF($A27="","",IF(OR($N27="Yes",$S27="Yes",$X27="Yes",$AC27="Yes",$AH27="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN28" s="68">
-        <f>IF($A28="","",IFERROR(IF($AI28&lt;&gt;"",$AI28,IF($AD28&lt;&gt;"",$AD28,IF($Y28&lt;&gt;"",$Y28,IF($T28&lt;&gt;"",$T28,IF($O28&lt;&gt;"",$O28,""))))),""))</f>
+        <f>IF($A27="","",IFERROR(IF($AI27&lt;&gt;"",$AI27,IF($AD27&lt;&gt;"",$AD27,IF($Y27&lt;&gt;"",$Y27,IF($T27&lt;&gt;"",$T27,IF($O27&lt;&gt;"",$O27,""))))),""))</f>
         <v/>
       </c>
       <c r="AO28" s="68">
-        <f>IFERROR(IF($AJ28&lt;&gt;"",$AJ28,IF($AE28&lt;&gt;"",$AE28,IF($Z28&lt;&gt;"",$Z28,IF($U28&lt;&gt;"",$U28,IF($P28&lt;&gt;"",$P28,""))))),"")</f>
-        <v/>
-      </c>
-      <c r="AP28" s="69" t="n"/>
-    </row>
-    <row r="29" ht="102.2" customHeight="1" s="41">
-      <c r="A29" s="64">
-        <f>IF(C29="","",$C$2&amp;"."&amp;COUNTA($C$8:C29)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="B29" s="71" t="inlineStr">
-        <is>
-          <t>REQ-NTF-001</t>
-        </is>
-      </c>
-      <c r="C29" s="40" t="inlineStr">
-        <is>
-          <t>QA xác nhận app STG (2026-07-28) · C-ORD-06 Resolved (mở rộng sang màn Thông báo)</t>
-        </is>
-      </c>
-      <c r="D29" s="40" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E29" s="40" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F29" s="72" t="inlineStr">
-        <is>
-          <t>Check hiển thị đúng khi màn Thông báo chưa có thông báo nào</t>
-        </is>
-      </c>
-      <c r="G29" s="72" t="inlineStr">
-        <is>
-          <t>Tài khoản chưa từng phát sinh sự kiện thông báo nào (danh sách Thông báo rỗng)</t>
-        </is>
-      </c>
-      <c r="H29" s="72" t="inlineStr">
-        <is>
-          <t>1. Đăng nhập tài khoản chưa có thông báo nào
-2. Mở màn Thông báo (icon chuông ở Header)</t>
-        </is>
-      </c>
-      <c r="I29" s="72" t="inlineStr">
-        <is>
-          <t>2. Hiển thị text "Hiện tại chưa có dữ liệu" (C-ORD-06, Resolved — QA xác nhận đúng UI thật)</t>
-        </is>
-      </c>
-      <c r="J29" s="64" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="K29" s="64" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L29" s="64" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+        <f>IFERROR(IF($AJ27&lt;&gt;"",$AJ27,IF($AE27&lt;&gt;"",$AE27,IF($Z27&lt;&gt;"",$Z27,IF($U27&lt;&gt;"",$U27,IF($P27&lt;&gt;"",$P27,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP28" s="69" t="inlineStr">
+        <is>
+          <t>Technique: EP-back-icon. Bổ sung 2026-07-30 theo yêu cầu user (QA GiangDC2 xác nhận trực tiếp trên app STG: icon quay lại tồn tại và hoạt động đúng ở màn này) — phát hiện khi quét lại toàn bộ TC-MASTER, kiểm tra completeness icon Back cho từng màn hình.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="41">
+      <c r="A29" s="64" t="n"/>
+      <c r="B29" s="70" t="inlineStr">
+        <is>
+          <t>Block Empty state (không có thông báo nào)</t>
+        </is>
+      </c>
+      <c r="C29" s="46" t="n"/>
+      <c r="D29" s="46" t="n"/>
+      <c r="E29" s="46" t="n"/>
+      <c r="F29" s="46" t="n"/>
+      <c r="G29" s="46" t="n"/>
+      <c r="H29" s="46" t="n"/>
+      <c r="I29" s="44" t="n"/>
+      <c r="J29" s="64" t="n"/>
+      <c r="K29" s="64" t="n"/>
+      <c r="L29" s="64" t="n"/>
       <c r="M29" s="64" t="n"/>
       <c r="N29" s="66" t="n"/>
       <c r="O29" s="66" t="n"/>
@@ -3483,40 +3485,80 @@
       <c r="AK29" s="67" t="n"/>
       <c r="AL29" s="67" t="n"/>
       <c r="AM29" s="68">
-        <f>IF($A29="","",IF(OR($N29="Yes",$S29="Yes",$X29="Yes",$AC29="Yes",$AH29="Yes"),"Yes","No"))</f>
+        <f>IF($A28="","",IF(OR($N28="Yes",$S28="Yes",$X28="Yes",$AC28="Yes",$AH28="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN29" s="68">
-        <f>IF($A29="","",IFERROR(IF($AI29&lt;&gt;"",$AI29,IF($AD29&lt;&gt;"",$AD29,IF($Y29&lt;&gt;"",$Y29,IF($T29&lt;&gt;"",$T29,IF($O29&lt;&gt;"",$O29,""))))),""))</f>
+        <f>IF($A28="","",IFERROR(IF($AI28&lt;&gt;"",$AI28,IF($AD28&lt;&gt;"",$AD28,IF($Y28&lt;&gt;"",$Y28,IF($T28&lt;&gt;"",$T28,IF($O28&lt;&gt;"",$O28,""))))),""))</f>
         <v/>
       </c>
       <c r="AO29" s="68">
-        <f>IFERROR(IF($AJ29&lt;&gt;"",$AJ29,IF($AE29&lt;&gt;"",$AE29,IF($Z29&lt;&gt;"",$Z29,IF($U29&lt;&gt;"",$U29,IF($P29&lt;&gt;"",$P29,""))))),"")</f>
-        <v/>
-      </c>
-      <c r="AP29" s="69" t="inlineStr">
-        <is>
-          <t>Text đã QA xác nhận trực tiếp trên UI thật (2026-07-28), mở rộng phạm vi C-ORD-06 sang màn Thông báo — Resolved | Technique: N/A — 0-dim (pure display state, không input/range/condition/param trong phạm vi SC này)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="41">
-      <c r="A30" s="64" t="n"/>
-      <c r="B30" s="70" t="inlineStr">
-        <is>
-          <t>Block Đánh dấu đã đọc</t>
-        </is>
-      </c>
-      <c r="C30" s="46" t="n"/>
-      <c r="D30" s="46" t="n"/>
-      <c r="E30" s="46" t="n"/>
-      <c r="F30" s="46" t="n"/>
-      <c r="G30" s="46" t="n"/>
-      <c r="H30" s="46" t="n"/>
-      <c r="I30" s="44" t="n"/>
-      <c r="J30" s="64" t="n"/>
-      <c r="K30" s="64" t="n"/>
-      <c r="L30" s="64" t="n"/>
+        <f>IFERROR(IF($AJ28&lt;&gt;"",$AJ28,IF($AE28&lt;&gt;"",$AE28,IF($Z28&lt;&gt;"",$Z28,IF($U28&lt;&gt;"",$U28,IF($P28&lt;&gt;"",$P28,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP29" s="69" t="n"/>
+    </row>
+    <row r="30" ht="102.2" customHeight="1" s="41">
+      <c r="A30" s="64">
+        <f>IF(C30="","",$C$2&amp;"."&amp;COUNTA($C$8:C30)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B30" s="71" t="inlineStr">
+        <is>
+          <t>REQ-NTF-001</t>
+        </is>
+      </c>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>QA xác nhận app STG (2026-07-28) · C-ORD-06 Resolved (mở rộng sang màn Thông báo)</t>
+        </is>
+      </c>
+      <c r="D30" s="40" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E30" s="40" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F30" s="72" t="inlineStr">
+        <is>
+          <t>Check hiển thị đúng khi màn Thông báo chưa có thông báo nào</t>
+        </is>
+      </c>
+      <c r="G30" s="72" t="inlineStr">
+        <is>
+          <t>Tài khoản chưa từng phát sinh sự kiện thông báo nào (danh sách Thông báo rỗng)</t>
+        </is>
+      </c>
+      <c r="H30" s="72" t="inlineStr">
+        <is>
+          <t>1. Đăng nhập tài khoản chưa có thông báo nào
+2. Mở màn Thông báo (icon chuông ở Header)</t>
+        </is>
+      </c>
+      <c r="I30" s="72" t="inlineStr">
+        <is>
+          <t>2. Hiển thị text "Hiện tại chưa có dữ liệu" (C-ORD-06, Resolved — QA xác nhận đúng UI thật)</t>
+        </is>
+      </c>
+      <c r="J30" s="64" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K30" s="64" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L30" s="64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="M30" s="64" t="n"/>
       <c r="N30" s="66" t="n"/>
       <c r="O30" s="66" t="n"/>
@@ -3544,80 +3586,40 @@
       <c r="AK30" s="67" t="n"/>
       <c r="AL30" s="67" t="n"/>
       <c r="AM30" s="68">
-        <f>IF($A30="","",IF(OR($N30="Yes",$S30="Yes",$X30="Yes",$AC30="Yes",$AH30="Yes"),"Yes","No"))</f>
+        <f>IF($A29="","",IF(OR($N29="Yes",$S29="Yes",$X29="Yes",$AC29="Yes",$AH29="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN30" s="68">
-        <f>IF($A30="","",IFERROR(IF($AI30&lt;&gt;"",$AI30,IF($AD30&lt;&gt;"",$AD30,IF($Y30&lt;&gt;"",$Y30,IF($T30&lt;&gt;"",$T30,IF($O30&lt;&gt;"",$O30,""))))),""))</f>
+        <f>IF($A29="","",IFERROR(IF($AI29&lt;&gt;"",$AI29,IF($AD29&lt;&gt;"",$AD29,IF($Y29&lt;&gt;"",$Y29,IF($T29&lt;&gt;"",$T29,IF($O29&lt;&gt;"",$O29,""))))),""))</f>
         <v/>
       </c>
       <c r="AO30" s="68">
-        <f>IFERROR(IF($AJ30&lt;&gt;"",$AJ30,IF($AE30&lt;&gt;"",$AE30,IF($Z30&lt;&gt;"",$Z30,IF($U30&lt;&gt;"",$U30,IF($P30&lt;&gt;"",$P30,""))))),"")</f>
-        <v/>
-      </c>
-      <c r="AP30" s="69" t="n"/>
-    </row>
-    <row r="31" ht="57.45" customHeight="1" s="41">
-      <c r="A31" s="64">
-        <f>IF(C31="","",$C$2&amp;"."&amp;COUNTA($C$8:C31)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="B31" s="64" t="inlineStr">
-        <is>
-          <t>REQ-NTF-001</t>
-        </is>
-      </c>
-      <c r="C31" s="64" t="inlineStr">
-        <is>
-          <t>DOC-v1.0-04 · QA đề xuất — Chờ BA/Dev — C-NTF-03 (Open)</t>
-        </is>
-      </c>
-      <c r="D31" s="64" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E31" s="64" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F31" s="65" t="inlineStr">
-        <is>
-          <t>Check bấm vào 1 thông báo cụ thể chuyển đúng trạng thái đã đọc (không ảnh hưởng thông báo khác)</t>
-        </is>
-      </c>
-      <c r="G31" s="65" t="inlineStr">
-        <is>
-          <t>Có ≥2 thông báo chưa đọc (chấm đỏ): thông báo A và thông báo B</t>
-        </is>
-      </c>
-      <c r="H31" s="65" t="inlineStr">
-        <is>
-          <t>1. Mở màn Thông báo, xác nhận thông báo A và B đều đang chưa đọc (có chấm đỏ)
-2. Bấm vào thông báo A</t>
-        </is>
-      </c>
-      <c r="I31" s="65" t="inlineStr">
-        <is>
-          <t>2. Thông báo A chuyển đã đọc (chấm đỏ biến mất); thông báo B vẫn giữ nguyên trạng thái chưa đọc (chấm đỏ còn)</t>
-        </is>
-      </c>
-      <c r="J31" s="64" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="K31" s="64" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L31" s="64" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+        <f>IFERROR(IF($AJ29&lt;&gt;"",$AJ29,IF($AE29&lt;&gt;"",$AE29,IF($Z29&lt;&gt;"",$Z29,IF($U29&lt;&gt;"",$U29,IF($P29&lt;&gt;"",$P29,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP30" s="69" t="inlineStr">
+        <is>
+          <t>Text đã QA xác nhận trực tiếp trên UI thật (2026-07-28), mở rộng phạm vi C-ORD-06 sang màn Thông báo — Resolved | Technique: N/A — 0-dim (pure display state, không input/range/condition/param trong phạm vi SC này)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="41">
+      <c r="A31" s="64" t="n"/>
+      <c r="B31" s="70" t="inlineStr">
+        <is>
+          <t>Block Đánh dấu đã đọc</t>
+        </is>
+      </c>
+      <c r="C31" s="46" t="n"/>
+      <c r="D31" s="46" t="n"/>
+      <c r="E31" s="46" t="n"/>
+      <c r="F31" s="46" t="n"/>
+      <c r="G31" s="46" t="n"/>
+      <c r="H31" s="46" t="n"/>
+      <c r="I31" s="44" t="n"/>
+      <c r="J31" s="64" t="n"/>
+      <c r="K31" s="64" t="n"/>
+      <c r="L31" s="64" t="n"/>
       <c r="M31" s="64" t="n"/>
       <c r="N31" s="66" t="n"/>
       <c r="O31" s="66" t="n"/>
@@ -3645,22 +3647,18 @@
       <c r="AK31" s="67" t="n"/>
       <c r="AL31" s="67" t="n"/>
       <c r="AM31" s="68">
-        <f>IF($A31="","",IF(OR($N31="Yes",$S31="Yes",$X31="Yes",$AC31="Yes",$AH31="Yes"),"Yes","No"))</f>
+        <f>IF($A30="","",IF(OR($N30="Yes",$S30="Yes",$X30="Yes",$AC30="Yes",$AH30="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN31" s="68">
-        <f>IF($A31="","",IFERROR(IF($AI31&lt;&gt;"",$AI31,IF($AD31&lt;&gt;"",$AD31,IF($Y31&lt;&gt;"",$Y31,IF($T31&lt;&gt;"",$T31,IF($O31&lt;&gt;"",$O31,""))))),""))</f>
+        <f>IF($A30="","",IFERROR(IF($AI30&lt;&gt;"",$AI30,IF($AD30&lt;&gt;"",$AD30,IF($Y30&lt;&gt;"",$Y30,IF($T30&lt;&gt;"",$T30,IF($O30&lt;&gt;"",$O30,""))))),""))</f>
         <v/>
       </c>
       <c r="AO31" s="68">
-        <f>IFERROR(IF($AJ31&lt;&gt;"",$AJ31,IF($AE31&lt;&gt;"",$AE31,IF($Z31&lt;&gt;"",$Z31,IF($U31&lt;&gt;"",$U31,IF($P31&lt;&gt;"",$P31,""))))),"")</f>
-        <v/>
-      </c>
-      <c r="AP31" s="69" t="inlineStr">
-        <is>
-          <t>Technique: ST-unread-read (valid, tap-single) | Hành vi suy luận theo UX chuẩn — C-NTF-03 (Open), cần BA/Dev confirm cơ chế thật</t>
-        </is>
-      </c>
+        <f>IFERROR(IF($AJ30&lt;&gt;"",$AJ30,IF($AE30&lt;&gt;"",$AE30,IF($Z30&lt;&gt;"",$Z30,IF($U30&lt;&gt;"",$U30,IF($P30&lt;&gt;"",$P30,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP31" s="69" t="n"/>
     </row>
     <row r="32" ht="57.45" customHeight="1" s="41">
       <c r="A32" s="64">
@@ -3689,23 +3687,23 @@
       </c>
       <c r="F32" s="65" t="inlineStr">
         <is>
-          <t>Check bấm nút "Đánh dấu đã đọc" chuyển TẤT CẢ thông báo sang đã đọc</t>
+          <t>Check bấm vào 1 thông báo cụ thể chuyển đúng trạng thái đã đọc (không ảnh hưởng thông báo khác)</t>
         </is>
       </c>
       <c r="G32" s="65" t="inlineStr">
         <is>
-          <t>Có ≥2 thông báo chưa đọc (chấm đỏ)</t>
+          <t>Có ≥2 thông báo chưa đọc (chấm đỏ): thông báo A và thông báo B</t>
         </is>
       </c>
       <c r="H32" s="65" t="inlineStr">
         <is>
-          <t>1. Mở màn Thông báo, xác nhận có ≥2 thông báo chưa đọc
-2. Bấm nút "Đánh dấu đã đọc" ở góc phải header</t>
+          <t>1. Mở màn Thông báo, xác nhận thông báo A và B đều đang chưa đọc (có chấm đỏ)
+2. Bấm vào thông báo A</t>
         </is>
       </c>
       <c r="I32" s="65" t="inlineStr">
         <is>
-          <t>2. TẤT CẢ thông báo trong danh sách chuyển đã đọc, không còn chấm đỏ nào</t>
+          <t>2. Thông báo A chuyển đã đọc (chấm đỏ biến mất); thông báo B vẫn giữ nguyên trạng thái chưa đọc (chấm đỏ còn)</t>
         </is>
       </c>
       <c r="J32" s="64" t="inlineStr">
@@ -3750,24 +3748,24 @@
       <c r="AK32" s="67" t="n"/>
       <c r="AL32" s="67" t="n"/>
       <c r="AM32" s="68">
-        <f>IF($A32="","",IF(OR($N32="Yes",$S32="Yes",$X32="Yes",$AC32="Yes",$AH32="Yes"),"Yes","No"))</f>
+        <f>IF($A31="","",IF(OR($N31="Yes",$S31="Yes",$X31="Yes",$AC31="Yes",$AH31="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN32" s="68">
-        <f>IF($A32="","",IFERROR(IF($AI32&lt;&gt;"",$AI32,IF($AD32&lt;&gt;"",$AD32,IF($Y32&lt;&gt;"",$Y32,IF($T32&lt;&gt;"",$T32,IF($O32&lt;&gt;"",$O32,""))))),""))</f>
+        <f>IF($A31="","",IFERROR(IF($AI31&lt;&gt;"",$AI31,IF($AD31&lt;&gt;"",$AD31,IF($Y31&lt;&gt;"",$Y31,IF($T31&lt;&gt;"",$T31,IF($O31&lt;&gt;"",$O31,""))))),""))</f>
         <v/>
       </c>
       <c r="AO32" s="68">
-        <f>IFERROR(IF($AJ32&lt;&gt;"",$AJ32,IF($AE32&lt;&gt;"",$AE32,IF($Z32&lt;&gt;"",$Z32,IF($U32&lt;&gt;"",$U32,IF($P32&lt;&gt;"",$P32,""))))),"")</f>
+        <f>IFERROR(IF($AJ31&lt;&gt;"",$AJ31,IF($AE31&lt;&gt;"",$AE31,IF($Z31&lt;&gt;"",$Z31,IF($U31&lt;&gt;"",$U31,IF($P31&lt;&gt;"",$P31,""))))),"")</f>
         <v/>
       </c>
       <c r="AP32" s="69" t="inlineStr">
         <is>
-          <t>Technique: ST-unread-read (valid, mark-all) | Hành vi suy luận theo UX chuẩn — C-NTF-03 (Open), cần BA/Dev confirm cơ chế thật</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="46.25" customHeight="1" s="41">
+          <t>Technique: ST-unread-read (valid, tap-single) | Hành vi suy luận theo UX chuẩn — C-NTF-03 (Open), cần BA/Dev confirm cơ chế thật</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="57.45" customHeight="1" s="41">
       <c r="A33" s="64">
         <f>IF(C33="","",$C$2&amp;"."&amp;COUNTA($C$8:C33)&amp;"")</f>
         <v/>
@@ -3779,7 +3777,7 @@
       </c>
       <c r="C33" s="64" t="inlineStr">
         <is>
-          <t>QA đề xuất — Chờ BA/Dev — C-NTF-03 (Open)</t>
+          <t>DOC-v1.0-04 · QA đề xuất — Chờ BA/Dev — C-NTF-03 (Open)</t>
         </is>
       </c>
       <c r="D33" s="64" t="inlineStr">
@@ -3794,23 +3792,23 @@
       </c>
       <c r="F33" s="65" t="inlineStr">
         <is>
-          <t>Check bấm vào 1 thông báo ĐÃ đọc không gây lỗi và không đổi trạng thái thông báo khác</t>
+          <t>Check bấm nút "Đánh dấu đã đọc" chuyển TẤT CẢ thông báo sang đã đọc</t>
         </is>
       </c>
       <c r="G33" s="65" t="inlineStr">
         <is>
-          <t>Có ≥1 thông báo đã ở trạng thái đã đọc (không chấm đỏ)</t>
+          <t>Có ≥2 thông báo chưa đọc (chấm đỏ)</t>
         </is>
       </c>
       <c r="H33" s="65" t="inlineStr">
         <is>
-          <t>1. Mở màn Thông báo, xác định 1 thông báo đã đọc
-2. Bấm vào thông báo đã đọc đó</t>
+          <t>1. Mở màn Thông báo, xác nhận có ≥2 thông báo chưa đọc
+2. Bấm nút "Đánh dấu đã đọc" ở góc phải header</t>
         </is>
       </c>
       <c r="I33" s="65" t="inlineStr">
         <is>
-          <t>2. Không có lỗi/crash; thông báo vẫn ở trạng thái đã đọc; các thông báo khác không đổi trạng thái</t>
+          <t>2. TẤT CẢ thông báo trong danh sách chuyển đã đọc, không còn chấm đỏ nào</t>
         </is>
       </c>
       <c r="J33" s="64" t="inlineStr">
@@ -3855,20 +3853,20 @@
       <c r="AK33" s="67" t="n"/>
       <c r="AL33" s="67" t="n"/>
       <c r="AM33" s="68">
-        <f>IF($A33="","",IF(OR($N33="Yes",$S33="Yes",$X33="Yes",$AC33="Yes",$AH33="Yes"),"Yes","No"))</f>
+        <f>IF($A32="","",IF(OR($N32="Yes",$S32="Yes",$X32="Yes",$AC32="Yes",$AH32="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN33" s="68">
-        <f>IF($A33="","",IFERROR(IF($AI33&lt;&gt;"",$AI33,IF($AD33&lt;&gt;"",$AD33,IF($Y33&lt;&gt;"",$Y33,IF($T33&lt;&gt;"",$T33,IF($O33&lt;&gt;"",$O33,""))))),""))</f>
+        <f>IF($A32="","",IFERROR(IF($AI32&lt;&gt;"",$AI32,IF($AD32&lt;&gt;"",$AD32,IF($Y32&lt;&gt;"",$Y32,IF($T32&lt;&gt;"",$T32,IF($O32&lt;&gt;"",$O32,""))))),""))</f>
         <v/>
       </c>
       <c r="AO33" s="68">
-        <f>IFERROR(IF($AJ33&lt;&gt;"",$AJ33,IF($AE33&lt;&gt;"",$AE33,IF($Z33&lt;&gt;"",$Z33,IF($U33&lt;&gt;"",$U33,IF($P33&lt;&gt;"",$P33,""))))),"")</f>
+        <f>IFERROR(IF($AJ32&lt;&gt;"",$AJ32,IF($AE32&lt;&gt;"",$AE32,IF($Z32&lt;&gt;"",$Z32,IF($U32&lt;&gt;"",$U32,IF($P32&lt;&gt;"",$P32,""))))),"")</f>
         <v/>
       </c>
       <c r="AP33" s="69" t="inlineStr">
         <is>
-          <t>Technique: ST-invalid(idempotent)-read-read (tap case) | C-NTF-03 (Open)</t>
+          <t>Technique: ST-unread-read (valid, mark-all) | Hành vi suy luận theo UX chuẩn — C-NTF-03 (Open), cần BA/Dev confirm cơ chế thật</t>
         </is>
       </c>
     </row>
@@ -3899,23 +3897,23 @@
       </c>
       <c r="F34" s="65" t="inlineStr">
         <is>
-          <t>Check bấm nút "Đánh dấu đã đọc" khi TOÀN BỘ thông báo đã đọc không gây lỗi</t>
+          <t>Check bấm vào 1 thông báo ĐÃ đọc không gây lỗi và không đổi trạng thái thông báo khác</t>
         </is>
       </c>
       <c r="G34" s="65" t="inlineStr">
         <is>
-          <t>Toàn bộ thông báo trong danh sách đã ở trạng thái đã đọc (không còn chấm đỏ nào)</t>
+          <t>Có ≥1 thông báo đã ở trạng thái đã đọc (không chấm đỏ)</t>
         </is>
       </c>
       <c r="H34" s="65" t="inlineStr">
         <is>
-          <t>1. Mở màn Thông báo, xác nhận không còn chấm đỏ nào
-2. Bấm nút "Đánh dấu đã đọc"</t>
+          <t>1. Mở màn Thông báo, xác định 1 thông báo đã đọc
+2. Bấm vào thông báo đã đọc đó</t>
         </is>
       </c>
       <c r="I34" s="65" t="inlineStr">
         <is>
-          <t>2. Không có lỗi/crash; danh sách giữ nguyên trạng thái đã đọc</t>
+          <t>2. Không có lỗi/crash; thông báo vẫn ở trạng thái đã đọc; các thông báo khác không đổi trạng thái</t>
         </is>
       </c>
       <c r="J34" s="64" t="inlineStr">
@@ -3960,40 +3958,84 @@
       <c r="AK34" s="67" t="n"/>
       <c r="AL34" s="67" t="n"/>
       <c r="AM34" s="68">
-        <f>IF($A34="","",IF(OR($N34="Yes",$S34="Yes",$X34="Yes",$AC34="Yes",$AH34="Yes"),"Yes","No"))</f>
+        <f>IF($A33="","",IF(OR($N33="Yes",$S33="Yes",$X33="Yes",$AC33="Yes",$AH33="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN34" s="68">
-        <f>IF($A34="","",IFERROR(IF($AI34&lt;&gt;"",$AI34,IF($AD34&lt;&gt;"",$AD34,IF($Y34&lt;&gt;"",$Y34,IF($T34&lt;&gt;"",$T34,IF($O34&lt;&gt;"",$O34,""))))),""))</f>
+        <f>IF($A33="","",IFERROR(IF($AI33&lt;&gt;"",$AI33,IF($AD33&lt;&gt;"",$AD33,IF($Y33&lt;&gt;"",$Y33,IF($T33&lt;&gt;"",$T33,IF($O33&lt;&gt;"",$O33,""))))),""))</f>
         <v/>
       </c>
       <c r="AO34" s="68">
-        <f>IFERROR(IF($AJ34&lt;&gt;"",$AJ34,IF($AE34&lt;&gt;"",$AE34,IF($Z34&lt;&gt;"",$Z34,IF($U34&lt;&gt;"",$U34,IF($P34&lt;&gt;"",$P34,""))))),"")</f>
+        <f>IFERROR(IF($AJ33&lt;&gt;"",$AJ33,IF($AE33&lt;&gt;"",$AE33,IF($Z33&lt;&gt;"",$Z33,IF($U33&lt;&gt;"",$U33,IF($P33&lt;&gt;"",$P33,""))))),"")</f>
         <v/>
       </c>
       <c r="AP34" s="69" t="inlineStr">
         <is>
-          <t>Technique: ST-invalid(idempotent)-read-read (mark-all case) | C-NTF-03 (Open)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="41">
-      <c r="A35" s="64" t="n"/>
-      <c r="B35" s="70" t="inlineStr">
-        <is>
-          <t>Block Load thêm dữ liệu (Scroll / Pagination)</t>
-        </is>
-      </c>
-      <c r="C35" s="46" t="n"/>
-      <c r="D35" s="46" t="n"/>
-      <c r="E35" s="46" t="n"/>
-      <c r="F35" s="46" t="n"/>
-      <c r="G35" s="46" t="n"/>
-      <c r="H35" s="46" t="n"/>
-      <c r="I35" s="44" t="n"/>
-      <c r="J35" s="64" t="n"/>
-      <c r="K35" s="64" t="n"/>
-      <c r="L35" s="64" t="n"/>
+          <t>Technique: ST-invalid(idempotent)-read-read (tap case) | C-NTF-03 (Open)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="46.25" customHeight="1" s="41">
+      <c r="A35" s="64">
+        <f>IF(C35="","",$C$2&amp;"."&amp;COUNTA($C$8:C35)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B35" s="64" t="inlineStr">
+        <is>
+          <t>REQ-NTF-001</t>
+        </is>
+      </c>
+      <c r="C35" s="64" t="inlineStr">
+        <is>
+          <t>QA đề xuất — Chờ BA/Dev — C-NTF-03 (Open)</t>
+        </is>
+      </c>
+      <c r="D35" s="64" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E35" s="64" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F35" s="65" t="inlineStr">
+        <is>
+          <t>Check bấm nút "Đánh dấu đã đọc" khi TOÀN BỘ thông báo đã đọc không gây lỗi</t>
+        </is>
+      </c>
+      <c r="G35" s="65" t="inlineStr">
+        <is>
+          <t>Toàn bộ thông báo trong danh sách đã ở trạng thái đã đọc (không còn chấm đỏ nào)</t>
+        </is>
+      </c>
+      <c r="H35" s="65" t="inlineStr">
+        <is>
+          <t>1. Mở màn Thông báo, xác nhận không còn chấm đỏ nào
+2. Bấm nút "Đánh dấu đã đọc"</t>
+        </is>
+      </c>
+      <c r="I35" s="65" t="inlineStr">
+        <is>
+          <t>2. Không có lỗi/crash; danh sách giữ nguyên trạng thái đã đọc</t>
+        </is>
+      </c>
+      <c r="J35" s="64" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K35" s="64" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L35" s="64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="M35" s="64" t="n"/>
       <c r="N35" s="66" t="n"/>
       <c r="O35" s="66" t="n"/>
@@ -4020,71 +4062,41 @@
       <c r="AJ35" s="67" t="n"/>
       <c r="AK35" s="67" t="n"/>
       <c r="AL35" s="67" t="n"/>
-      <c r="AM35" s="68" t="n"/>
-      <c r="AN35" s="68" t="n"/>
-      <c r="AO35" s="68" t="n"/>
-      <c r="AP35" s="69" t="n"/>
-    </row>
-    <row r="36" ht="57.45" customHeight="1" s="41">
-      <c r="A36" s="64">
-        <f>IF(C36="","",$C$2&amp;"."&amp;COUNTA($C$8:C36)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="B36" s="64" t="inlineStr">
-        <is>
-          <t>REQ-NTF-001</t>
-        </is>
-      </c>
-      <c r="C36" s="64" t="inlineStr">
-        <is>
-          <t>QA xác nhận app STG (2026-07-28) · C-NTF-03 Resolved (cơ chế phân trang)</t>
-        </is>
-      </c>
-      <c r="D36" s="64" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E36" s="64" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F36" s="65" t="inlineStr">
-        <is>
-          <t>Check load đúng batch dữ liệu đầu tiên khi mới mở màn Thông báo</t>
-        </is>
-      </c>
-      <c r="G36" s="65" t="inlineStr">
-        <is>
-          <t>Có nhiều hơn 1 "trang" dữ liệu thông báo (vd &gt; 20 thông báo tổng)</t>
-        </is>
-      </c>
-      <c r="H36" s="65" t="inlineStr">
-        <is>
-          <t>1. Mở màn Thông báo lần đầu (chưa scroll)</t>
-        </is>
-      </c>
-      <c r="I36" s="65" t="inlineStr">
-        <is>
-          <t>1. Hiển thị đúng batch thông báo đầu tiên (mới nhất trước), sắp xếp đúng nhóm Hôm nay/Hôm qua, chưa load các thông báo cũ hơn thuộc trang sau</t>
-        </is>
-      </c>
-      <c r="J36" s="64" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="K36" s="64" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L36" s="64" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="AM35" s="68">
+        <f>IF($A34="","",IF(OR($N34="Yes",$S34="Yes",$X34="Yes",$AC34="Yes",$AH34="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="AN35" s="68">
+        <f>IF($A34="","",IFERROR(IF($AI34&lt;&gt;"",$AI34,IF($AD34&lt;&gt;"",$AD34,IF($Y34&lt;&gt;"",$Y34,IF($T34&lt;&gt;"",$T34,IF($O34&lt;&gt;"",$O34,""))))),""))</f>
+        <v/>
+      </c>
+      <c r="AO35" s="68">
+        <f>IFERROR(IF($AJ34&lt;&gt;"",$AJ34,IF($AE34&lt;&gt;"",$AE34,IF($Z34&lt;&gt;"",$Z34,IF($U34&lt;&gt;"",$U34,IF($P34&lt;&gt;"",$P34,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP35" s="69" t="inlineStr">
+        <is>
+          <t>Technique: ST-invalid(idempotent)-read-read (mark-all case) | C-NTF-03 (Open)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="41">
+      <c r="A36" s="64" t="n"/>
+      <c r="B36" s="70" t="inlineStr">
+        <is>
+          <t>Block Load thêm dữ liệu (Scroll / Pagination)</t>
+        </is>
+      </c>
+      <c r="C36" s="46" t="n"/>
+      <c r="D36" s="46" t="n"/>
+      <c r="E36" s="46" t="n"/>
+      <c r="F36" s="46" t="n"/>
+      <c r="G36" s="46" t="n"/>
+      <c r="H36" s="46" t="n"/>
+      <c r="I36" s="44" t="n"/>
+      <c r="J36" s="64" t="n"/>
+      <c r="K36" s="64" t="n"/>
+      <c r="L36" s="64" t="n"/>
       <c r="M36" s="64" t="n"/>
       <c r="N36" s="66" t="n"/>
       <c r="O36" s="66" t="n"/>
@@ -4111,25 +4123,12 @@
       <c r="AJ36" s="67" t="n"/>
       <c r="AK36" s="67" t="n"/>
       <c r="AL36" s="67" t="n"/>
-      <c r="AM36" s="68">
-        <f>IF($A36="","",IF(OR($N36="Yes",$S36="Yes",$X36="Yes",$AC36="Yes",$AH36="Yes"),"Yes","No"))</f>
-        <v/>
-      </c>
-      <c r="AN36" s="68">
-        <f>IF($A36="","",IFERROR(IF($AI36&lt;&gt;"",$AI36,IF($AD36&lt;&gt;"",$AD36,IF($Y36&lt;&gt;"",$Y36,IF($T36&lt;&gt;"",$T36,IF($O36&lt;&gt;"",$O36,""))))),""))</f>
-        <v/>
-      </c>
-      <c r="AO36" s="68">
-        <f>IFERROR(IF($AJ36&lt;&gt;"",$AJ36,IF($AE36&lt;&gt;"",$AE36,IF($Z36&lt;&gt;"",$Z36,IF($U36&lt;&gt;"",$U36,IF($P36&lt;&gt;"",$P36,""))))),"")</f>
-        <v/>
-      </c>
-      <c r="AP36" s="69" t="inlineStr">
-        <is>
-          <t>Technique: BVA-page1 (initial load) | Cơ chế phân trang — C-NTF-03 (Resolved, QA xác nhận đúng UI thật 2026-07-28)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="46.25" customHeight="1" s="41">
+      <c r="AM36" s="68" t="n"/>
+      <c r="AN36" s="68" t="n"/>
+      <c r="AO36" s="68" t="n"/>
+      <c r="AP36" s="69" t="n"/>
+    </row>
+    <row r="37" ht="57.45" customHeight="1" s="41">
       <c r="A37" s="64">
         <f>IF(C37="","",$C$2&amp;"."&amp;COUNTA($C$8:C37)&amp;"")</f>
         <v/>
@@ -4141,7 +4140,7 @@
       </c>
       <c r="C37" s="64" t="inlineStr">
         <is>
-          <t>UI nền tảng (scroll-load) · QA đề xuất — Chờ BA/Dev — C-NTF-03 (Open)</t>
+          <t>QA xác nhận app STG (2026-07-28) · C-NTF-03 Resolved (cơ chế phân trang)</t>
         </is>
       </c>
       <c r="D37" s="64" t="inlineStr">
@@ -4156,22 +4155,22 @@
       </c>
       <c r="F37" s="65" t="inlineStr">
         <is>
-          <t>Check scroll xuống cuối danh sách hiện tại tự động load thêm batch tiếp theo</t>
+          <t>Check load đúng batch dữ liệu đầu tiên khi mới mở màn Thông báo</t>
         </is>
       </c>
       <c r="G37" s="65" t="inlineStr">
         <is>
-          <t>Đã ở màn Thông báo với batch đầu tiên hiển thị, còn dữ liệu cũ hơn chưa load</t>
+          <t>Có nhiều hơn 1 "trang" dữ liệu thông báo (vd &gt; 20 thông báo tổng)</t>
         </is>
       </c>
       <c r="H37" s="65" t="inlineStr">
         <is>
-          <t>1. Scroll xuống tới cuối danh sách đang hiển thị</t>
+          <t>1. Mở màn Thông báo lần đầu (chưa scroll)</t>
         </is>
       </c>
       <c r="I37" s="65" t="inlineStr">
         <is>
-          <t>1. Hệ thống tự động load thêm batch thông báo cũ hơn tiếp theo, nối liền danh sách hiện tại, không trùng lặp thông báo đã hiển thị trước đó</t>
+          <t>1. Hiển thị đúng batch thông báo đầu tiên (mới nhất trước), sắp xếp đúng nhóm Hôm nay/Hôm qua, chưa load các thông báo cũ hơn thuộc trang sau</t>
         </is>
       </c>
       <c r="J37" s="64" t="inlineStr">
@@ -4216,24 +4215,24 @@
       <c r="AK37" s="67" t="n"/>
       <c r="AL37" s="67" t="n"/>
       <c r="AM37" s="68">
-        <f>IF($A37="","",IF(OR($N37="Yes",$S37="Yes",$X37="Yes",$AC37="Yes",$AH37="Yes"),"Yes","No"))</f>
+        <f>IF($A36="","",IF(OR($N36="Yes",$S36="Yes",$X36="Yes",$AC36="Yes",$AH36="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN37" s="68">
-        <f>IF($A37="","",IFERROR(IF($AI37&lt;&gt;"",$AI37,IF($AD37&lt;&gt;"",$AD37,IF($Y37&lt;&gt;"",$Y37,IF($T37&lt;&gt;"",$T37,IF($O37&lt;&gt;"",$O37,""))))),""))</f>
+        <f>IF($A36="","",IFERROR(IF($AI36&lt;&gt;"",$AI36,IF($AD36&lt;&gt;"",$AD36,IF($Y36&lt;&gt;"",$Y36,IF($T36&lt;&gt;"",$T36,IF($O36&lt;&gt;"",$O36,""))))),""))</f>
         <v/>
       </c>
       <c r="AO37" s="68">
-        <f>IFERROR(IF($AJ37&lt;&gt;"",$AJ37,IF($AE37&lt;&gt;"",$AE37,IF($Z37&lt;&gt;"",$Z37,IF($U37&lt;&gt;"",$U37,IF($P37&lt;&gt;"",$P37,""))))),"")</f>
+        <f>IFERROR(IF($AJ36&lt;&gt;"",$AJ36,IF($AE36&lt;&gt;"",$AE36,IF($Z36&lt;&gt;"",$Z36,IF($U36&lt;&gt;"",$U36,IF($P36&lt;&gt;"",$P36,""))))),"")</f>
         <v/>
       </c>
       <c r="AP37" s="69" t="inlineStr">
         <is>
-          <t>Technique: BVA-page2 (load-more) | C-NTF-03 (Open)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="35.05" customHeight="1" s="41">
+          <t>Technique: BVA-page1 (initial load) | Cơ chế phân trang — C-NTF-03 (Resolved, QA xác nhận đúng UI thật 2026-07-28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="46.25" customHeight="1" s="41">
       <c r="A38" s="64">
         <f>IF(C38="","",$C$2&amp;"."&amp;COUNTA($C$8:C38)&amp;"")</f>
         <v/>
@@ -4260,22 +4259,22 @@
       </c>
       <c r="F38" s="65" t="inlineStr">
         <is>
-          <t>Check khi đã load hết toàn bộ dữ liệu, hiển thị rõ ràng không còn gì để load thêm</t>
+          <t>Check scroll xuống cuối danh sách hiện tại tự động load thêm batch tiếp theo</t>
         </is>
       </c>
       <c r="G38" s="65" t="inlineStr">
         <is>
-          <t>Đã scroll load hết toàn bộ thông báo (không còn dữ liệu cũ hơn)</t>
+          <t>Đã ở màn Thông báo với batch đầu tiên hiển thị, còn dữ liệu cũ hơn chưa load</t>
         </is>
       </c>
       <c r="H38" s="65" t="inlineStr">
         <is>
-          <t>1. Scroll tới cuối danh sách khi đã ở batch cuối cùng</t>
+          <t>1. Scroll xuống tới cuối danh sách đang hiển thị</t>
         </is>
       </c>
       <c r="I38" s="65" t="inlineStr">
         <is>
-          <t>1. Không xuất hiện loading spinner treo mãi; hệ thống nhận biết đã hết dữ liệu (không gọi thêm request load)</t>
+          <t>1. Hệ thống tự động load thêm batch thông báo cũ hơn tiếp theo, nối liền danh sách hiện tại, không trùng lặp thông báo đã hiển thị trước đó</t>
         </is>
       </c>
       <c r="J38" s="64" t="inlineStr">
@@ -4320,20 +4319,20 @@
       <c r="AK38" s="67" t="n"/>
       <c r="AL38" s="67" t="n"/>
       <c r="AM38" s="68">
-        <f>IF($A38="","",IF(OR($N38="Yes",$S38="Yes",$X38="Yes",$AC38="Yes",$AH38="Yes"),"Yes","No"))</f>
+        <f>IF($A37="","",IF(OR($N37="Yes",$S37="Yes",$X37="Yes",$AC37="Yes",$AH37="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN38" s="68">
-        <f>IF($A38="","",IFERROR(IF($AI38&lt;&gt;"",$AI38,IF($AD38&lt;&gt;"",$AD38,IF($Y38&lt;&gt;"",$Y38,IF($T38&lt;&gt;"",$T38,IF($O38&lt;&gt;"",$O38,""))))),""))</f>
+        <f>IF($A37="","",IFERROR(IF($AI37&lt;&gt;"",$AI37,IF($AD37&lt;&gt;"",$AD37,IF($Y37&lt;&gt;"",$Y37,IF($T37&lt;&gt;"",$T37,IF($O37&lt;&gt;"",$O37,""))))),""))</f>
         <v/>
       </c>
       <c r="AO38" s="68">
-        <f>IFERROR(IF($AJ38&lt;&gt;"",$AJ38,IF($AE38&lt;&gt;"",$AE38,IF($Z38&lt;&gt;"",$Z38,IF($U38&lt;&gt;"",$U38,IF($P38&lt;&gt;"",$P38,""))))),"")</f>
+        <f>IFERROR(IF($AJ37&lt;&gt;"",$AJ37,IF($AE37&lt;&gt;"",$AE37,IF($Z37&lt;&gt;"",$Z37,IF($U37&lt;&gt;"",$U37,IF($P37&lt;&gt;"",$P37,""))))),"")</f>
         <v/>
       </c>
       <c r="AP38" s="69" t="inlineStr">
         <is>
-          <t>Technique: BVA-last-page | C-NTF-03 (Open)</t>
+          <t>Technique: BVA-page2 (load-more) | C-NTF-03 (Open)</t>
         </is>
       </c>
     </row>
@@ -4364,22 +4363,22 @@
       </c>
       <c r="F39" s="65" t="inlineStr">
         <is>
-          <t>Check tiếp tục scroll sau khi đã hết dữ liệu không gây lỗi/trùng lặp</t>
+          <t>Check khi đã load hết toàn bộ dữ liệu, hiển thị rõ ràng không còn gì để load thêm</t>
         </is>
       </c>
       <c r="G39" s="65" t="inlineStr">
         <is>
-          <t>Đã load hết toàn bộ dữ liệu thông báo (như TC load hết dữ liệu)</t>
+          <t>Đã scroll load hết toàn bộ thông báo (không còn dữ liệu cũ hơn)</t>
         </is>
       </c>
       <c r="H39" s="65" t="inlineStr">
         <is>
-          <t>1. Tiếp tục kéo/scroll thêm nhiều lần sau khi đã hết dữ liệu</t>
+          <t>1. Scroll tới cuối danh sách khi đã ở batch cuối cùng</t>
         </is>
       </c>
       <c r="I39" s="65" t="inlineStr">
         <is>
-          <t>1. Không có thông báo bị lặp lại trong danh sách; không phát sinh lỗi/crash/treo app</t>
+          <t>1. Không xuất hiện loading spinner treo mãi; hệ thống nhận biết đã hết dữ liệu (không gọi thêm request load)</t>
         </is>
       </c>
       <c r="J39" s="64" t="inlineStr">
@@ -4424,20 +4423,20 @@
       <c r="AK39" s="67" t="n"/>
       <c r="AL39" s="67" t="n"/>
       <c r="AM39" s="68">
-        <f>IF($A39="","",IF(OR($N39="Yes",$S39="Yes",$X39="Yes",$AC39="Yes",$AH39="Yes"),"Yes","No"))</f>
+        <f>IF($A38="","",IF(OR($N38="Yes",$S38="Yes",$X38="Yes",$AC38="Yes",$AH38="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN39" s="68">
-        <f>IF($A39="","",IFERROR(IF($AI39&lt;&gt;"",$AI39,IF($AD39&lt;&gt;"",$AD39,IF($Y39&lt;&gt;"",$Y39,IF($T39&lt;&gt;"",$T39,IF($O39&lt;&gt;"",$O39,""))))),""))</f>
+        <f>IF($A38="","",IFERROR(IF($AI38&lt;&gt;"",$AI38,IF($AD38&lt;&gt;"",$AD38,IF($Y38&lt;&gt;"",$Y38,IF($T38&lt;&gt;"",$T38,IF($O38&lt;&gt;"",$O38,""))))),""))</f>
         <v/>
       </c>
       <c r="AO39" s="68">
-        <f>IFERROR(IF($AJ39&lt;&gt;"",$AJ39,IF($AE39&lt;&gt;"",$AE39,IF($Z39&lt;&gt;"",$Z39,IF($U39&lt;&gt;"",$U39,IF($P39&lt;&gt;"",$P39,""))))),"")</f>
+        <f>IFERROR(IF($AJ38&lt;&gt;"",$AJ38,IF($AE38&lt;&gt;"",$AE38,IF($Z38&lt;&gt;"",$Z38,IF($U38&lt;&gt;"",$U38,IF($P38&lt;&gt;"",$P38,""))))),"")</f>
         <v/>
       </c>
       <c r="AP39" s="69" t="inlineStr">
         <is>
-          <t>Technique: BVA-max+1 (over-scroll) | C-NTF-03 (Open)</t>
+          <t>Technique: BVA-last-page | C-NTF-03 (Open)</t>
         </is>
       </c>
     </row>
@@ -4468,23 +4467,22 @@
       </c>
       <c r="F40" s="65" t="inlineStr">
         <is>
-          <t>Check mất kết nối mạng đúng lúc đang load thêm dữ liệu không làm mất dữ liệu đã hiển thị</t>
+          <t>Check tiếp tục scroll sau khi đã hết dữ liệu không gây lỗi/trùng lặp</t>
         </is>
       </c>
       <c r="G40" s="65" t="inlineStr">
         <is>
-          <t>Đang trong quá trình scroll load thêm batch tiếp theo</t>
+          <t>Đã load hết toàn bộ dữ liệu thông báo (như TC load hết dữ liệu)</t>
         </is>
       </c>
       <c r="H40" s="65" t="inlineStr">
         <is>
-          <t>1. Ngắt kết nối mạng đúng lúc hệ thống đang load thêm dữ liệu (giữa lúc scroll)
-2. Quan sát màn Thông báo</t>
+          <t>1. Tiếp tục kéo/scroll thêm nhiều lần sau khi đã hết dữ liệu</t>
         </is>
       </c>
       <c r="I40" s="65" t="inlineStr">
         <is>
-          <t>2. Hiển thị thông báo lỗi/cho phép thử lại (không crash); danh sách thông báo đã load trước đó KHÔNG bị mất/xoá</t>
+          <t>1. Không có thông báo bị lặp lại trong danh sách; không phát sinh lỗi/crash/treo app</t>
         </is>
       </c>
       <c r="J40" s="64" t="inlineStr">
@@ -4529,36 +4527,84 @@
       <c r="AK40" s="67" t="n"/>
       <c r="AL40" s="67" t="n"/>
       <c r="AM40" s="68">
-        <f>IF($A40="","",IF(OR($N40="Yes",$S40="Yes",$X40="Yes",$AC40="Yes",$AH40="Yes"),"Yes","No"))</f>
+        <f>IF($A39="","",IF(OR($N39="Yes",$S39="Yes",$X39="Yes",$AC39="Yes",$AH39="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN40" s="68">
-        <f>IF($A40="","",IFERROR(IF($AI40&lt;&gt;"",$AI40,IF($AD40&lt;&gt;"",$AD40,IF($Y40&lt;&gt;"",$Y40,IF($T40&lt;&gt;"",$T40,IF($O40&lt;&gt;"",$O40,""))))),""))</f>
+        <f>IF($A39="","",IFERROR(IF($AI39&lt;&gt;"",$AI39,IF($AD39&lt;&gt;"",$AD39,IF($Y39&lt;&gt;"",$Y39,IF($T39&lt;&gt;"",$T39,IF($O39&lt;&gt;"",$O39,""))))),""))</f>
         <v/>
       </c>
       <c r="AO40" s="68">
-        <f>IFERROR(IF($AJ40&lt;&gt;"",$AJ40,IF($AE40&lt;&gt;"",$AE40,IF($Z40&lt;&gt;"",$Z40,IF($U40&lt;&gt;"",$U40,IF($P40&lt;&gt;"",$P40,""))))),"")</f>
+        <f>IFERROR(IF($AJ39&lt;&gt;"",$AJ39,IF($AE39&lt;&gt;"",$AE39,IF($Z39&lt;&gt;"",$Z39,IF($U39&lt;&gt;"",$U39,IF($P39&lt;&gt;"",$P39,""))))),"")</f>
         <v/>
       </c>
       <c r="AP40" s="69" t="inlineStr">
         <is>
-          <t>Technique: EP-network-error (edge case khi load thêm) | C-NTF-03 (Open)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="41">
-      <c r="A41" s="64" t="n"/>
-      <c r="B41" s="64" t="n"/>
-      <c r="C41" s="64" t="n"/>
-      <c r="D41" s="64" t="n"/>
-      <c r="E41" s="64" t="n"/>
-      <c r="F41" s="65" t="n"/>
-      <c r="G41" s="65" t="n"/>
-      <c r="H41" s="65" t="n"/>
-      <c r="I41" s="65" t="n"/>
-      <c r="J41" s="64" t="n"/>
-      <c r="K41" s="64" t="n"/>
-      <c r="L41" s="64" t="n"/>
+          <t>Technique: BVA-max+1 (over-scroll) | C-NTF-03 (Open)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="35.05" customHeight="1" s="41">
+      <c r="A41" s="64">
+        <f>IF(C41="","",$C$2&amp;"."&amp;COUNTA($C$8:C41)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B41" s="64" t="inlineStr">
+        <is>
+          <t>REQ-NTF-001</t>
+        </is>
+      </c>
+      <c r="C41" s="64" t="inlineStr">
+        <is>
+          <t>UI nền tảng (scroll-load) · QA đề xuất — Chờ BA/Dev — C-NTF-03 (Open)</t>
+        </is>
+      </c>
+      <c r="D41" s="64" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E41" s="64" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F41" s="65" t="inlineStr">
+        <is>
+          <t>Check mất kết nối mạng đúng lúc đang load thêm dữ liệu không làm mất dữ liệu đã hiển thị</t>
+        </is>
+      </c>
+      <c r="G41" s="65" t="inlineStr">
+        <is>
+          <t>Đang trong quá trình scroll load thêm batch tiếp theo</t>
+        </is>
+      </c>
+      <c r="H41" s="65" t="inlineStr">
+        <is>
+          <t>1. Ngắt kết nối mạng đúng lúc hệ thống đang load thêm dữ liệu (giữa lúc scroll)
+2. Quan sát màn Thông báo</t>
+        </is>
+      </c>
+      <c r="I41" s="65" t="inlineStr">
+        <is>
+          <t>2. Hiển thị thông báo lỗi/cho phép thử lại (không crash); danh sách thông báo đã load trước đó KHÔNG bị mất/xoá</t>
+        </is>
+      </c>
+      <c r="J41" s="64" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K41" s="64" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L41" s="64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="M41" s="64" t="n"/>
       <c r="N41" s="66" t="n"/>
       <c r="O41" s="66" t="n"/>
@@ -4585,21 +4631,38 @@
       <c r="AJ41" s="67" t="n"/>
       <c r="AK41" s="67" t="n"/>
       <c r="AL41" s="67" t="n"/>
-      <c r="AM41" s="68" t="n"/>
-      <c r="AN41" s="68" t="n"/>
-      <c r="AO41" s="68" t="n"/>
-      <c r="AP41" s="69" t="n"/>
+      <c r="AM41" s="68">
+        <f>IF($A40="","",IF(OR($N40="Yes",$S40="Yes",$X40="Yes",$AC40="Yes",$AH40="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="AN41" s="68">
+        <f>IF($A40="","",IFERROR(IF($AI40&lt;&gt;"",$AI40,IF($AD40&lt;&gt;"",$AD40,IF($Y40&lt;&gt;"",$Y40,IF($T40&lt;&gt;"",$T40,IF($O40&lt;&gt;"",$O40,""))))),""))</f>
+        <v/>
+      </c>
+      <c r="AO41" s="68">
+        <f>IFERROR(IF($AJ40&lt;&gt;"",$AJ40,IF($AE40&lt;&gt;"",$AE40,IF($Z40&lt;&gt;"",$Z40,IF($U40&lt;&gt;"",$U40,IF($P40&lt;&gt;"",$P40,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP41" s="69" t="inlineStr">
+        <is>
+          <t>Technique: EP-network-error (edge case khi load thêm) | C-NTF-03 (Open)</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="41">
       <c r="A42" s="64" t="n"/>
-      <c r="B42" s="64" t="n"/>
-      <c r="C42" s="64" t="n"/>
-      <c r="D42" s="64" t="n"/>
-      <c r="E42" s="64" t="n"/>
-      <c r="F42" s="65" t="n"/>
-      <c r="G42" s="65" t="n"/>
-      <c r="H42" s="65" t="n"/>
-      <c r="I42" s="65" t="n"/>
+      <c r="B42" s="70" t="inlineStr">
+        <is>
+          <t>Block Kiểm soát nội dung push (OPR-07)</t>
+        </is>
+      </c>
+      <c r="C42" s="46" t="n"/>
+      <c r="D42" s="46" t="n"/>
+      <c r="E42" s="46" t="n"/>
+      <c r="F42" s="46" t="n"/>
+      <c r="G42" s="46" t="n"/>
+      <c r="H42" s="46" t="n"/>
+      <c r="I42" s="44" t="n"/>
       <c r="J42" s="64" t="n"/>
       <c r="K42" s="64" t="n"/>
       <c r="L42" s="64" t="n"/>
@@ -4635,18 +4698,67 @@
       <c r="AP42" s="69" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="41">
-      <c r="A43" s="64" t="n"/>
-      <c r="B43" s="64" t="n"/>
-      <c r="C43" s="64" t="n"/>
-      <c r="D43" s="64" t="n"/>
-      <c r="E43" s="64" t="n"/>
-      <c r="F43" s="65" t="n"/>
-      <c r="G43" s="65" t="n"/>
-      <c r="H43" s="65" t="n"/>
-      <c r="I43" s="65" t="n"/>
-      <c r="J43" s="64" t="n"/>
-      <c r="K43" s="64" t="n"/>
-      <c r="L43" s="64" t="n"/>
+      <c r="A43" s="64">
+        <f>IF(C43="","",$C$2&amp;"."&amp;COUNTA($C$8:C43)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B43" s="64" t="inlineStr">
+        <is>
+          <t>REQ-NTF-002</t>
+        </is>
+      </c>
+      <c r="C43" s="64" t="inlineStr">
+        <is>
+          <t>DOC-v1.0-01 §D7 (OPR-07)</t>
+        </is>
+      </c>
+      <c r="D43" s="64" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E43" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F43" s="65" t="inlineStr">
+        <is>
+          <t>Check nội dung push "SĐT đã lộ" (NTF-01) KHÔNG hiển thị số điện thoại</t>
+        </is>
+      </c>
+      <c r="G43" s="65" t="inlineStr">
+        <is>
+          <t>Đơn vừa chuyển MATCHED (Carrier bấm "Tôi mang giúp được"), SĐT 2 bên đã lộ TRONG APP (theo REQ-ASN-002/003)</t>
+        </is>
+      </c>
+      <c r="H43" s="65" t="inlineStr">
+        <is>
+          <t>1. Trigger sự kiện ghép đơn (Carrier bấm "Tôi mang giúp được")
+2. Quan sát nội dung push notification "SĐT đã lộ" hiển thị trên thiết bị (title + body), KHÔNG mở app
+3. Đối chiếu text với SĐT thật của bên còn lại</t>
+        </is>
+      </c>
+      <c r="I43" s="65" t="inlineStr">
+        <is>
+          <t>3. Title và body của push notification KHÔNG chứa chuỗi số điện thoại (dạng số hoặc định dạng SĐT) của bên còn lại — SĐT chỉ xem được sau khi bấm vào thông báo để mở app</t>
+        </is>
+      </c>
+      <c r="J43" s="64" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K43" s="64" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L43" s="64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="M43" s="64" t="n"/>
       <c r="N43" s="66" t="n"/>
       <c r="O43" s="66" t="n"/>
@@ -4673,24 +4785,86 @@
       <c r="AJ43" s="67" t="n"/>
       <c r="AK43" s="67" t="n"/>
       <c r="AL43" s="67" t="n"/>
-      <c r="AM43" s="68" t="n"/>
-      <c r="AN43" s="68" t="n"/>
-      <c r="AO43" s="68" t="n"/>
-      <c r="AP43" s="69" t="n"/>
+      <c r="AM43" s="68">
+        <f>IF($A36="","",IF(OR($N36="Yes",$S36="Yes",$X36="Yes",$AC36="Yes",$AH36="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="AN43" s="68">
+        <f>IF($A36="","",IFERROR(IF($AI36&lt;&gt;"",$AI36,IF($AD36&lt;&gt;"",$AD36,IF($Y36&lt;&gt;"",$Y36,IF($T36&lt;&gt;"",$T36,IF($O36&lt;&gt;"",$O36,""))))),""))</f>
+        <v/>
+      </c>
+      <c r="AO43" s="68">
+        <f>IFERROR(IF($AJ36&lt;&gt;"",$AJ36,IF($AE36&lt;&gt;"",$AE36,IF($Z36&lt;&gt;"",$Z36,IF($U36&lt;&gt;"",$U36,IF($P36&lt;&gt;"",$P36,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP43" s="69" t="inlineStr">
+        <is>
+          <t>Technique: EP-push-content-hidden (baseline) | ⚠ Chưa có ảnh/bằng chứng UI cho nội dung push thật (không có trong DOC-v1.0-04) — TC assert theo đúng RULE (OPR-07), cần vibe-test xác nhận nội dung push thật trên thiết bị trước khi coi Expected là final. Test riêng biệt với SC-ASN-003 (SĐT không lộ TRONG APP trước khi ghép) — TC này test tầng NỘI DUNG PUSH, khác bề mặt.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="41">
-      <c r="A44" s="64" t="n"/>
-      <c r="B44" s="64" t="n"/>
-      <c r="C44" s="64" t="n"/>
-      <c r="D44" s="64" t="n"/>
-      <c r="E44" s="64" t="n"/>
-      <c r="F44" s="65" t="n"/>
-      <c r="G44" s="65" t="n"/>
-      <c r="H44" s="65" t="n"/>
-      <c r="I44" s="65" t="n"/>
-      <c r="J44" s="64" t="n"/>
-      <c r="K44" s="64" t="n"/>
-      <c r="L44" s="64" t="n"/>
+      <c r="A44" s="64">
+        <f>IF(C44="","",$C$2&amp;"."&amp;COUNTA($C$8:C44)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B44" s="64" t="inlineStr">
+        <is>
+          <t>REQ-NTF-002</t>
+        </is>
+      </c>
+      <c r="C44" s="64" t="inlineStr">
+        <is>
+          <t>DOC-v1.0-01 §D7 (OPR-07)</t>
+        </is>
+      </c>
+      <c r="D44" s="64" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E44" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F44" s="65" t="inlineStr">
+        <is>
+          <t>Check nội dung push ở mốc sau (NTF-04 "Đã lấy hàng") vẫn KHÔNG hiển thị SĐT</t>
+        </is>
+      </c>
+      <c r="G44" s="65" t="inlineStr">
+        <is>
+          <t>Đơn đã MATCHED từ trước, Carrier vừa bấm "Tôi đã lấy hàng"</t>
+        </is>
+      </c>
+      <c r="H44" s="65" t="inlineStr">
+        <is>
+          <t>1. Carrier bấm "Tôi đã lấy hàng" trên đơn đã MATCHED
+2. Quan sát nội dung push notification tương ứng (NTF-04) trên thiết bị, KHÔNG mở app
+3. Đối chiếu text với SĐT thật của 2 bên</t>
+        </is>
+      </c>
+      <c r="I44" s="65" t="inlineStr">
+        <is>
+          <t>3. Title và body của push notification KHÔNG chứa SĐT của bất kỳ bên nào — rule áp dụng NHẤT QUÁN ở mọi mốc thông báo trong vòng đời đơn (NTF-04/05/06/08/09), không chỉ lúc vừa ghép</t>
+        </is>
+      </c>
+      <c r="J44" s="64" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K44" s="64" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L44" s="64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="M44" s="64" t="n"/>
       <c r="N44" s="66" t="n"/>
       <c r="O44" s="66" t="n"/>
@@ -4717,10 +4891,23 @@
       <c r="AJ44" s="67" t="n"/>
       <c r="AK44" s="67" t="n"/>
       <c r="AL44" s="67" t="n"/>
-      <c r="AM44" s="68" t="n"/>
-      <c r="AN44" s="68" t="n"/>
-      <c r="AO44" s="68" t="n"/>
-      <c r="AP44" s="69" t="n"/>
+      <c r="AM44" s="68">
+        <f>IF($A36="","",IF(OR($N36="Yes",$S36="Yes",$X36="Yes",$AC36="Yes",$AH36="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="AN44" s="68">
+        <f>IF($A36="","",IFERROR(IF($AI36&lt;&gt;"",$AI36,IF($AD36&lt;&gt;"",$AD36,IF($Y36&lt;&gt;"",$Y36,IF($T36&lt;&gt;"",$T36,IF($O36&lt;&gt;"",$O36,""))))),""))</f>
+        <v/>
+      </c>
+      <c r="AO44" s="68">
+        <f>IFERROR(IF($AJ36&lt;&gt;"",$AJ36,IF($AE36&lt;&gt;"",$AE36,IF($Z36&lt;&gt;"",$Z36,IF($U36&lt;&gt;"",$U36,IF($P36&lt;&gt;"",$P36,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP44" s="69" t="inlineStr">
+        <is>
+          <t>Technique: EP-push-content-hidden-later-lifecycle | Đối chứng cho TC trước (mốc vừa ghép) — xác nhận rule không chỉ áp dụng tại thời điểm MATCHED mà xuyên suốt các mốc thông báo khác. Cùng cảnh báo cần vibe-test như TC trước.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="41">
       <c r="A45" s="64" t="n"/>
@@ -8676,6 +8863,7 @@
   <autoFilter ref="A6:U6"/>
   <mergeCells count="25">
     <mergeCell ref="A7:I7"/>
+    <mergeCell ref="B31:I31"/>
     <mergeCell ref="AH5:AL5"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="A5:C5"/>
@@ -8687,18 +8875,17 @@
     <mergeCell ref="N5:R5"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="B29:I29"/>
     <mergeCell ref="D5:I5"/>
-    <mergeCell ref="B28:I28"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="X5:AB5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
-    <mergeCell ref="B30:I30"/>
     <mergeCell ref="AM5:AP5"/>
     <mergeCell ref="S5:W5"/>
     <mergeCell ref="C4:E4"/>
-    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="B36:I36"/>
     <mergeCell ref="B26:I26"/>
   </mergeCells>
   <dataValidations count="8">
@@ -8747,7 +8934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="40" min="1" max="1"/>
@@ -9408,29 +9595,159 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="76" t="inlineStr">
+        <is>
+          <t>SC-NTF-010</t>
+        </is>
+      </c>
+      <c r="B11" s="77" t="inlineStr">
+        <is>
+          <t>Nội dung push không chứa SĐT (kiểm soát lộ liên hệ, OPR-07)</t>
+        </is>
+      </c>
+      <c r="C11" s="77" t="inlineStr">
+        <is>
+          <t>DOC-v1.0-01 §D7 "OPR-07 ... không đưa SĐT vào nội dung push"</t>
+        </is>
+      </c>
+      <c r="D11" s="78" t="inlineStr">
+        <is>
+          <t>✅ 2 (EP-push-content-hidden-baseline / EP-push-content-hidden-later-lifecycle)</t>
+        </is>
+      </c>
+      <c r="E11" s="78" t="inlineStr">
+        <is>
+          <t>N/A: single condition (có/không chứa SĐT), không có ≥2 điều kiện nhân</t>
+        </is>
+      </c>
+      <c r="F11" s="79" t="inlineStr">
+        <is>
+          <t>N/A: single condition (có/không chứa SĐT), không có ≥2 điều kiện nhân</t>
+        </is>
+      </c>
+      <c r="G11" s="79" t="inlineStr">
+        <is>
+          <t>N/A: single condition (có/không chứa SĐT), không có ≥2 điều kiện nhân</t>
+        </is>
+      </c>
+      <c r="H11" s="79" t="inlineStr">
+        <is>
+          <t>N/A: single condition (có/không chứa SĐT), không có ≥2 điều kiện nhân</t>
+        </is>
+      </c>
+      <c r="I11" s="79" t="inlineStr">
+        <is>
+          <t>N/A: single condition (có/không chứa SĐT), không có ≥2 điều kiện nhân</t>
+        </is>
+      </c>
+      <c r="J11" s="79" t="inlineStr">
+        <is>
+          <t>N/A: single condition (có/không chứa SĐT), không có ≥2 điều kiện nhân</t>
+        </is>
+      </c>
+      <c r="K11" s="79" t="inlineStr">
+        <is>
+          <t>N/A: single condition (có/không chứa SĐT), không có ≥2 điều kiện nhân</t>
+        </is>
+      </c>
+      <c r="L11" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="78" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
+    </row>
     <row r="12" ht="15" customHeight="1" s="41">
-      <c r="A12" s="82" t="inlineStr">
-        <is>
-          <t>Total scenarios: 9 (8 NTF còn hiệu lực + SC-ASN-013; SC-NTF-006 đã DEPRECATED 2026-07-29 nên không còn row riêng)</t>
+      <c r="A12" s="76" t="inlineStr">
+        <is>
+          <t>SC-NTF-011</t>
+        </is>
+      </c>
+      <c r="B12" s="77" t="inlineStr">
+        <is>
+          <t>Icon quay lại tại màn Thông báo</t>
+        </is>
+      </c>
+      <c r="C12" s="77" t="inlineStr">
+        <is>
+          <t>Quan sát thực tế app STG (QA GiangDC2, chat 2026-07-30)</t>
+        </is>
+      </c>
+      <c r="D12" s="78" t="inlineStr">
+        <is>
+          <t>N/A: display/navigation-only, không có input/condition để áp dụng technique</t>
+        </is>
+      </c>
+      <c r="E12" s="78" t="inlineStr">
+        <is>
+          <t>N/A: display/navigation-only, không có input/condition để áp dụng technique</t>
+        </is>
+      </c>
+      <c r="F12" s="79" t="inlineStr">
+        <is>
+          <t>N/A: display/navigation-only, không có input/condition để áp dụng technique</t>
+        </is>
+      </c>
+      <c r="G12" s="79" t="inlineStr">
+        <is>
+          <t>N/A: display/navigation-only, không có input/condition để áp dụng technique</t>
+        </is>
+      </c>
+      <c r="H12" s="79" t="inlineStr">
+        <is>
+          <t>N/A: display/navigation-only, không có input/condition để áp dụng technique</t>
+        </is>
+      </c>
+      <c r="I12" s="79" t="inlineStr">
+        <is>
+          <t>N/A: display/navigation-only, không có input/condition để áp dụng technique</t>
+        </is>
+      </c>
+      <c r="J12" s="79" t="inlineStr">
+        <is>
+          <t>N/A: display/navigation-only, không có input/condition để áp dụng technique</t>
+        </is>
+      </c>
+      <c r="K12" s="79" t="inlineStr">
+        <is>
+          <t>N/A: display/navigation-only, không có input/condition để áp dụng technique</t>
+        </is>
+      </c>
+      <c r="L12" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="78" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="41">
       <c r="A13" s="82" t="inlineStr">
         <is>
-          <t>Total TCs derived (per-scenario rubric, chưa gồm Step 3b completeness TC): 27</t>
+          <t>Total scenarios: 10 (8 NTF còn hiệu lực + SC-ASN-013 + SC-NTF-010 [NEW 2026-07-30, OPR-07]; SC-NTF-006 đã DEPRECATED 2026-07-29 nên không còn row riêng)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="41">
       <c r="A14" s="82" t="inlineStr">
         <is>
-          <t>Most-applied technique: B4 ST (SC-NTF-003: 6, SC-NTF-008: 4) / B2 BVA (SC-NTF-006: 3, SC-NTF-009: 4)</t>
+          <t>Total TCs derived (per-scenario rubric, chưa gồm Step 3b completeness TC): 30</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="41">
       <c r="A15" s="82" t="inlineStr">
+        <is>
+          <t>Most-applied technique: B4 ST (SC-NTF-003: 6, SC-NTF-008: 4) / B2 BVA (SC-NTF-006: 3, SC-NTF-009: 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="82" t="inlineStr">
         <is>
           <t>Least-applied technique: B3 DT, B5 PW, B7 CRUD, B8 CEG — N/A toàn bộ 9 scenario (lý do log tại từng cột)</t>
         </is>
